--- a/assets/documentos/Formato_de_Verificacion_Alineacion_de_Informacion_Estrategica.xlsx
+++ b/assets/documentos/Formato_de_Verificacion_Alineacion_de_Informacion_Estrategica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jglezlezo\Desktop\1. JOSS\01. 2026\01. VERIFICACIONES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33795A2-AEC5-4E9A-A473-EAE85B1BB7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC55426E-CE32-4C00-AF0E-57EFEE5ED871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -482,9 +482,6 @@
     <t xml:space="preserve">                          FORMATO DE VERIFICACIÓN DE ALINEACIÓN DE INFORMACIÓN ESTRATÉGICA </t>
   </si>
   <si>
-    <t>Folio CP:</t>
-  </si>
-  <si>
     <t>Lic. Mariana Zurizadaí Torres Torres
 Directora de Planeación.</t>
   </si>
@@ -497,6 +494,9 @@
   <si>
     <t xml:space="preserve">Fecha de actualización: 03-02-2026
 </t>
+  </si>
+  <si>
+    <t>Folio DP:</t>
   </si>
 </sst>
 </file>
@@ -1305,15 +1305,114 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1335,9 +1434,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1391,102 +1487,6 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1550,7 +1550,7 @@
       <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="47625"/>
-          <a:ext cx="2695575" cy="781051"/>
+          <a:ext cx="2857500" cy="781051"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1878,7 +1878,7 @@
   <dimension ref="B1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="0.85546875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="3.85546875" style="5" customWidth="1"/>
     <col min="2" max="2" width="11.140625" style="5" customWidth="1"/>
     <col min="3" max="3" width="17.140625" style="5" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" style="5" customWidth="1"/>
@@ -1891,91 +1891,92 @@
     <col min="11" max="11" width="11.7109375" style="5" customWidth="1"/>
     <col min="12" max="12" width="15.5703125" style="5" customWidth="1"/>
     <col min="13" max="13" width="13.85546875" style="5" customWidth="1"/>
-    <col min="14" max="16384" width="10.85546875" style="5"/>
+    <col min="14" max="14" width="4" style="5" customWidth="1"/>
+    <col min="15" max="16384" width="10.85546875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="94" t="s">
+      <c r="B2" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="96"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="89"/>
     </row>
     <row r="3" spans="2:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="97"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
-      <c r="M3" s="99"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="92"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B4" s="97"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="99"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="91"/>
+      <c r="M4" s="92"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="100" t="s">
+      <c r="B5" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="101"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="94"/>
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
+      <c r="K5" s="94"/>
+      <c r="L5" s="94"/>
+      <c r="M5" s="95"/>
     </row>
     <row r="6" spans="2:13" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="102"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="103"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="103"/>
-      <c r="K6" s="103"/>
-      <c r="L6" s="103"/>
-      <c r="M6" s="104"/>
+      <c r="B6" s="96"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="97"/>
+      <c r="M6" s="98"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" s="7"/>
       <c r="C7" s="8"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="91"/>
       <c r="H7" s="41"/>
       <c r="I7" s="41"/>
       <c r="J7" s="2"/>
@@ -1984,65 +1985,65 @@
       <c r="M7" s="9"/>
     </row>
     <row r="8" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="108" t="s">
+      <c r="B8" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="109"/>
-      <c r="D8" s="109"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
       <c r="E8" s="41"/>
-      <c r="F8" s="115" t="s">
+      <c r="F8" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="115"/>
-      <c r="H8" s="115"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
       <c r="I8" s="41"/>
-      <c r="J8" s="112" t="s">
+      <c r="J8" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="K8" s="113"/>
-      <c r="L8" s="113"/>
-      <c r="M8" s="114"/>
+      <c r="K8" s="72"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="73"/>
     </row>
     <row r="9" spans="2:13" s="48" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B9" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="110" t="s">
+      <c r="C9" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="111"/>
+      <c r="D9" s="70"/>
       <c r="E9" s="49"/>
       <c r="F9" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="116" t="s">
+      <c r="G9" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="116"/>
+      <c r="H9" s="76"/>
       <c r="I9" s="49"/>
       <c r="J9" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="110" t="s">
+      <c r="K9" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="L9" s="111"/>
+      <c r="L9" s="70"/>
       <c r="M9" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:13" ht="59.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="24"/>
-      <c r="C10" s="123"/>
-      <c r="D10" s="124"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="86"/>
       <c r="E10" s="1"/>
       <c r="F10" s="45"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="93"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
       <c r="I10" s="1"/>
       <c r="J10" s="46"/>
-      <c r="K10" s="93"/>
-      <c r="L10" s="93"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="74"/>
       <c r="M10" s="25"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.3">
@@ -2055,10 +2056,10 @@
       <c r="H11" s="34"/>
       <c r="I11" s="34"/>
       <c r="J11" s="35"/>
-      <c r="K11" s="93" t="s">
+      <c r="K11" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="L11" s="93"/>
+      <c r="L11" s="74"/>
       <c r="M11" s="25">
         <f>M10</f>
         <v>0</v>
@@ -2079,20 +2080,20 @@
       <c r="M12" s="18"/>
     </row>
     <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="66"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="79"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="109"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="110"/>
+      <c r="H13" s="110"/>
+      <c r="I13" s="110"/>
+      <c r="J13" s="110"/>
+      <c r="K13" s="110"/>
+      <c r="L13" s="110"/>
+      <c r="M13" s="111"/>
     </row>
     <row r="14" spans="2:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="10"/>
@@ -2109,20 +2110,20 @@
       <c r="M14" s="13"/>
     </row>
     <row r="15" spans="2:13" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="65" t="s">
+      <c r="B15" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="66"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="71"/>
-      <c r="M15" s="72"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="104"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="104"/>
+      <c r="K15" s="104"/>
+      <c r="L15" s="104"/>
+      <c r="M15" s="105"/>
     </row>
     <row r="16" spans="2:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="7"/>
@@ -2139,20 +2140,20 @@
       <c r="M16" s="14"/>
     </row>
     <row r="17" spans="2:13" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="69"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="71"/>
-      <c r="M17" s="72"/>
+      <c r="C17" s="102"/>
+      <c r="D17" s="103"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="104"/>
+      <c r="K17" s="104"/>
+      <c r="L17" s="104"/>
+      <c r="M17" s="105"/>
     </row>
     <row r="18" spans="2:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="30"/>
@@ -2169,40 +2170,40 @@
       <c r="M18" s="14"/>
     </row>
     <row r="19" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="83" t="s">
+      <c r="B19" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="84"/>
-      <c r="D19" s="117" t="s">
+      <c r="C19" s="116"/>
+      <c r="D19" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="118"/>
-      <c r="F19" s="119"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="79"/>
       <c r="G19" s="59"/>
       <c r="H19" s="63"/>
       <c r="I19" s="47"/>
-      <c r="J19" s="87" t="s">
+      <c r="J19" s="119" t="s">
         <v>16</v>
       </c>
-      <c r="K19" s="88"/>
+      <c r="K19" s="120"/>
       <c r="L19" s="61" t="s">
         <v>22</v>
       </c>
       <c r="M19" s="58"/>
     </row>
     <row r="20" spans="2:13" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="85"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="120" t="s">
+      <c r="B20" s="117"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="121"/>
-      <c r="F20" s="122"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="82"/>
       <c r="G20" s="57"/>
       <c r="H20" s="63"/>
       <c r="I20" s="47"/>
-      <c r="J20" s="89"/>
-      <c r="K20" s="90"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="122"/>
       <c r="L20" s="62" t="s">
         <v>23</v>
       </c>
@@ -2237,20 +2238,20 @@
       <c r="M22" s="15"/>
     </row>
     <row r="23" spans="2:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="80" t="s">
+      <c r="B23" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="81"/>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="81"/>
-      <c r="L23" s="81"/>
-      <c r="M23" s="82"/>
+      <c r="C23" s="113"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="113"/>
+      <c r="G23" s="113"/>
+      <c r="H23" s="113"/>
+      <c r="I23" s="113"/>
+      <c r="J23" s="113"/>
+      <c r="K23" s="113"/>
+      <c r="L23" s="113"/>
+      <c r="M23" s="114"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="23"/>
@@ -2268,20 +2269,20 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="23"/>
-      <c r="C25" s="74" t="s">
+      <c r="C25" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
+      <c r="D25" s="94"/>
+      <c r="E25" s="94"/>
+      <c r="F25" s="94"/>
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
       <c r="I25" s="22"/>
-      <c r="J25" s="74" t="s">
+      <c r="J25" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="K25" s="74"/>
-      <c r="L25" s="74"/>
+      <c r="K25" s="94"/>
+      <c r="L25" s="94"/>
       <c r="M25" s="53"/>
     </row>
     <row r="26" spans="2:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2314,53 +2315,53 @@
     </row>
     <row r="28" spans="2:13" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="23"/>
-      <c r="C28" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
-      <c r="J28" s="73" t="s">
+      <c r="C28" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="K28" s="73"/>
-      <c r="L28" s="73"/>
+      <c r="D28" s="108"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="108"/>
+      <c r="J28" s="106" t="s">
+        <v>26</v>
+      </c>
+      <c r="K28" s="106"/>
+      <c r="L28" s="106"/>
       <c r="M28" s="56"/>
     </row>
     <row r="29" spans="2:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="105" t="s">
+      <c r="B29" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="106"/>
-      <c r="D29" s="106"/>
-      <c r="E29" s="106"/>
-      <c r="F29" s="106"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="106"/>
-      <c r="I29" s="106"/>
-      <c r="J29" s="106"/>
-      <c r="K29" s="106"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="107"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="65"/>
+      <c r="M29" s="66"/>
     </row>
     <row r="30" spans="2:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="91" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="92"/>
-      <c r="D30" s="92"/>
-      <c r="E30" s="92"/>
-      <c r="F30" s="92"/>
+      <c r="B30" s="123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="124"/>
+      <c r="D30" s="124"/>
+      <c r="E30" s="124"/>
+      <c r="F30" s="124"/>
       <c r="G30" s="37"/>
       <c r="H30" s="37"/>
       <c r="I30" s="37"/>
-      <c r="J30" s="75"/>
-      <c r="K30" s="75"/>
+      <c r="J30" s="107"/>
+      <c r="K30" s="107"/>
       <c r="L30" s="39" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M30" s="40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.3">
@@ -2368,11 +2369,11 @@
       <c r="M31" s="27"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B32" s="67"/>
-      <c r="C32" s="67"/>
+      <c r="B32" s="100"/>
+      <c r="C32" s="100"/>
       <c r="D32" s="29"/>
-      <c r="F32" s="64"/>
-      <c r="G32" s="64"/>
+      <c r="F32" s="99"/>
+      <c r="G32" s="99"/>
       <c r="H32" s="26"/>
       <c r="I32" s="26"/>
       <c r="J32" s="44"/>
@@ -2382,20 +2383,8 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B29:M29"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="D15:M15"/>
     <mergeCell ref="B2:M4"/>
     <mergeCell ref="B5:M5"/>
     <mergeCell ref="B6:M6"/>
@@ -2412,15 +2401,27 @@
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="D13:M13"/>
     <mergeCell ref="B23:M23"/>
+    <mergeCell ref="B29:M29"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K11:L11"/>
     <mergeCell ref="B19:C20"/>
     <mergeCell ref="J19:K20"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="D15:M15"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup scale="93" fitToWidth="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="89" fitToWidth="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
   <extLst>
